--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/95.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/95.xlsx
@@ -426,13 +426,13 @@
         <v>-15.42939325423831</v>
       </c>
       <c r="E2">
-        <v>-10.14835761263695</v>
+        <v>-8.992170271368593</v>
       </c>
       <c r="F2">
-        <v>-2.67616529710173</v>
+        <v>-2.597931794479137</v>
       </c>
       <c r="G2">
-        <v>-9.511380564999115</v>
+        <v>-9.003496531637364</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-15.36937801914077</v>
       </c>
       <c r="E3">
-        <v>-10.98841218342984</v>
+        <v>-9.625862281631944</v>
       </c>
       <c r="F3">
-        <v>-2.277305564286366</v>
+        <v>-2.960108933596331</v>
       </c>
       <c r="G3">
-        <v>-9.397232954805043</v>
+        <v>-9.005747702604069</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-15.36910954584374</v>
       </c>
       <c r="E4">
-        <v>-11.41068785617109</v>
+        <v>-10.67705242455846</v>
       </c>
       <c r="F4">
-        <v>-2.124060079870666</v>
+        <v>-2.557627578495927</v>
       </c>
       <c r="G4">
-        <v>-9.85757424367732</v>
+        <v>-9.587069567663471</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-15.40415430322634</v>
       </c>
       <c r="E5">
-        <v>-11.40495027960337</v>
+        <v>-11.67333482014197</v>
       </c>
       <c r="F5">
-        <v>-1.935719982067962</v>
+        <v>-2.560631238698478</v>
       </c>
       <c r="G5">
-        <v>-9.556496679608301</v>
+        <v>-9.865804259887948</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-15.48011359881252</v>
       </c>
       <c r="E6">
-        <v>-12.48348787706221</v>
+        <v>-11.61722249871292</v>
       </c>
       <c r="F6">
-        <v>-1.870486877464903</v>
+        <v>-2.342965278101866</v>
       </c>
       <c r="G6">
-        <v>-9.752610086809188</v>
+        <v>-9.447208950265882</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-15.56445760546501</v>
       </c>
       <c r="E7">
-        <v>-13.65946917821809</v>
+        <v>-12.25753513797549</v>
       </c>
       <c r="F7">
-        <v>-1.59135357047836</v>
+        <v>-2.327796214221801</v>
       </c>
       <c r="G7">
-        <v>-9.339794989698689</v>
+        <v>-9.659080554233698</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-15.6634855960001</v>
       </c>
       <c r="E8">
-        <v>-14.30841761741329</v>
+        <v>-12.30899218812465</v>
       </c>
       <c r="F8">
-        <v>-1.782515916022402</v>
+        <v>-2.150552097779597</v>
       </c>
       <c r="G8">
-        <v>-9.536378494366151</v>
+        <v>-9.755182380693201</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-15.74428038249087</v>
       </c>
       <c r="E9">
-        <v>-15.22946394583336</v>
+        <v>-14.13619522242757</v>
       </c>
       <c r="F9">
-        <v>-1.613518197075066</v>
+        <v>-1.777738721210457</v>
       </c>
       <c r="G9">
-        <v>-9.314859960696898</v>
+        <v>-9.326211821351059</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-15.81168185164101</v>
       </c>
       <c r="E10">
-        <v>-15.7963202082175</v>
+        <v>-15.15387465769733</v>
       </c>
       <c r="F10">
-        <v>-1.431037970279766</v>
+        <v>-2.1188032603325</v>
       </c>
       <c r="G10">
-        <v>-9.180604096897294</v>
+        <v>-9.548154104849338</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-15.8319998326773</v>
       </c>
       <c r="E11">
-        <v>-16.77572950964843</v>
+        <v>-14.94915593323257</v>
       </c>
       <c r="F11">
-        <v>-1.256952418744436</v>
+        <v>-1.706919106842919</v>
       </c>
       <c r="G11">
-        <v>-8.937186304485762</v>
+        <v>-9.067774083827853</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-15.81400016991496</v>
       </c>
       <c r="E12">
-        <v>-17.0499421962349</v>
+        <v>-15.75424615621224</v>
       </c>
       <c r="F12">
-        <v>-1.0624484390975</v>
+        <v>-1.503858920292467</v>
       </c>
       <c r="G12">
-        <v>-8.837095270651437</v>
+        <v>-7.826574418607683</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-15.73535461379787</v>
       </c>
       <c r="E13">
-        <v>-18.63887504215024</v>
+        <v>-16.51238968915439</v>
       </c>
       <c r="F13">
-        <v>-0.9501226476452903</v>
+        <v>-1.561863690938697</v>
       </c>
       <c r="G13">
-        <v>-7.43044447101511</v>
+        <v>-7.65774652774147</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-15.62501285786209</v>
       </c>
       <c r="E14">
-        <v>-19.18755853834161</v>
+        <v>-17.541204642009</v>
       </c>
       <c r="F14">
-        <v>-1.06994930592985</v>
+        <v>-1.141206298286066</v>
       </c>
       <c r="G14">
-        <v>-7.566891915961711</v>
+        <v>-7.24856640963309</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-15.48591840099486</v>
       </c>
       <c r="E15">
-        <v>-19.80401517653176</v>
+        <v>-18.71971736013517</v>
       </c>
       <c r="F15">
-        <v>-0.4503371155750422</v>
+        <v>-1.019245765571895</v>
       </c>
       <c r="G15">
-        <v>-6.837714466027379</v>
+        <v>-7.332223895410473</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-15.36895176861467</v>
       </c>
       <c r="E16">
-        <v>-20.2555040350965</v>
+        <v>-18.70963244852009</v>
       </c>
       <c r="F16">
-        <v>-0.4058769803319871</v>
+        <v>-0.4569259498969094</v>
       </c>
       <c r="G16">
-        <v>-7.491620042035303</v>
+        <v>-6.614547280679568</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-15.29090498479233</v>
       </c>
       <c r="E17">
-        <v>-22.10659024131588</v>
+        <v>-21.09127919795214</v>
       </c>
       <c r="F17">
-        <v>0.1097949817891499</v>
+        <v>-0.4569996745957586</v>
       </c>
       <c r="G17">
-        <v>-6.724682509680043</v>
+        <v>-6.617384418206724</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-15.29817418321288</v>
       </c>
       <c r="E18">
-        <v>-22.36844472233541</v>
+        <v>-21.15735416219806</v>
       </c>
       <c r="F18">
-        <v>0.3850589846372172</v>
+        <v>0.120012065335279</v>
       </c>
       <c r="G18">
-        <v>-6.44474939997035</v>
+        <v>-6.011074555416902</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-15.38588068143926</v>
       </c>
       <c r="E19">
-        <v>-23.59562042214801</v>
+        <v>-22.12983942687126</v>
       </c>
       <c r="F19">
-        <v>0.8124352652939549</v>
+        <v>0.4950040481737816</v>
       </c>
       <c r="G19">
-        <v>-6.026223611804608</v>
+        <v>-5.582580714632416</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-15.56257506606556</v>
       </c>
       <c r="E20">
-        <v>-24.3280512796746</v>
+        <v>-23.08518441742543</v>
       </c>
       <c r="F20">
-        <v>0.9923019929334228</v>
+        <v>0.9433338822843329</v>
       </c>
       <c r="G20">
-        <v>-5.744284311498117</v>
+        <v>-5.733892509050344</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-15.78551234429996</v>
       </c>
       <c r="E21">
-        <v>-24.63301683324715</v>
+        <v>-22.81941733486327</v>
       </c>
       <c r="F21">
-        <v>1.324717548002836</v>
+        <v>1.272959495941118</v>
       </c>
       <c r="G21">
-        <v>-5.445673103855855</v>
+        <v>-5.86582436988138</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-16.03889156503724</v>
       </c>
       <c r="E22">
-        <v>-25.15182598640992</v>
+        <v>-23.83186185418015</v>
       </c>
       <c r="F22">
-        <v>2.005294265734077</v>
+        <v>1.225316773136507</v>
       </c>
       <c r="G22">
-        <v>-5.712532869230967</v>
+        <v>-5.695063120420232</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-16.27944248984774</v>
       </c>
       <c r="E23">
-        <v>-26.09839932281123</v>
+        <v>-23.71237806748777</v>
       </c>
       <c r="F23">
-        <v>2.082653840746717</v>
+        <v>1.588855748263904</v>
       </c>
       <c r="G23">
-        <v>-6.159691565765865</v>
+        <v>-5.986212358416976</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-16.50250130683308</v>
       </c>
       <c r="E24">
-        <v>-26.16764874733652</v>
+        <v>-24.61731661386256</v>
       </c>
       <c r="F24">
-        <v>2.137402299132542</v>
+        <v>1.673760093581242</v>
       </c>
       <c r="G24">
-        <v>-5.708401308397956</v>
+        <v>-5.901204170059571</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-16.68286461072941</v>
       </c>
       <c r="E25">
-        <v>-26.90342614715479</v>
+        <v>-25.33006672335182</v>
       </c>
       <c r="F25">
-        <v>2.406608451163936</v>
+        <v>2.058435691358471</v>
       </c>
       <c r="G25">
-        <v>-5.87699746107642</v>
+        <v>-5.223290517800852</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-16.82878039993747</v>
       </c>
       <c r="E26">
-        <v>-27.38723925318627</v>
+        <v>-24.30615157937351</v>
       </c>
       <c r="F26">
-        <v>2.340211490359945</v>
+        <v>1.998463548130592</v>
       </c>
       <c r="G26">
-        <v>-6.694205627445513</v>
+        <v>-6.245163230498768</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-16.92642803042245</v>
       </c>
       <c r="E27">
-        <v>-27.9028377182776</v>
+        <v>-24.77739817003371</v>
       </c>
       <c r="F27">
-        <v>2.199922500491432</v>
+        <v>1.970497864612081</v>
       </c>
       <c r="G27">
-        <v>-6.285823350812097</v>
+        <v>-6.162975626940822</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-16.98975625540765</v>
       </c>
       <c r="E28">
-        <v>-26.512125236626</v>
+        <v>-24.96345505311285</v>
       </c>
       <c r="F28">
-        <v>2.418432567471497</v>
+        <v>1.945590513544705</v>
       </c>
       <c r="G28">
-        <v>-6.550998048507719</v>
+        <v>-6.676722636452621</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-17.00681157782799</v>
       </c>
       <c r="E29">
-        <v>-26.30139269867906</v>
+        <v>-25.45329555804855</v>
       </c>
       <c r="F29">
-        <v>2.507538392255834</v>
+        <v>2.247692791876073</v>
       </c>
       <c r="G29">
-        <v>-6.226653970388703</v>
+        <v>-6.116962354490492</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-16.98587507668035</v>
       </c>
       <c r="E30">
-        <v>-26.28926997376053</v>
+        <v>-24.40060196175149</v>
       </c>
       <c r="F30">
-        <v>2.325267742413442</v>
+        <v>1.825349671558746</v>
       </c>
       <c r="G30">
-        <v>-6.780938610028878</v>
+        <v>-5.997948242353693</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-16.9111379540028</v>
       </c>
       <c r="E31">
-        <v>-26.77191926197204</v>
+        <v>-25.05601706182964</v>
       </c>
       <c r="F31">
-        <v>2.011174017559147</v>
+        <v>1.913769608133565</v>
       </c>
       <c r="G31">
-        <v>-6.403311301455292</v>
+        <v>-6.307232648814564</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-16.79078456713724</v>
       </c>
       <c r="E32">
-        <v>-25.9767011123291</v>
+        <v>-24.35346054733164</v>
       </c>
       <c r="F32">
-        <v>2.037509474028949</v>
+        <v>1.658460147651535</v>
       </c>
       <c r="G32">
-        <v>-5.887111177698893</v>
+        <v>-6.171685672254644</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-16.61458087340046</v>
       </c>
       <c r="E33">
-        <v>-24.99959227569406</v>
+        <v>-23.89463103240047</v>
       </c>
       <c r="F33">
-        <v>1.624500397606366</v>
+        <v>1.603862452133019</v>
       </c>
       <c r="G33">
-        <v>-6.006704635305065</v>
+        <v>-5.967299211751119</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-16.39552029454376</v>
       </c>
       <c r="E34">
-        <v>-25.0714636866698</v>
+        <v>-23.66388716781364</v>
       </c>
       <c r="F34">
-        <v>2.029583654718964</v>
+        <v>1.469295824283045</v>
       </c>
       <c r="G34">
-        <v>-5.877619843637802</v>
+        <v>-6.020165313467741</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-16.12861740806339</v>
       </c>
       <c r="E35">
-        <v>-24.89137080385876</v>
+        <v>-23.19979556608556</v>
       </c>
       <c r="F35">
-        <v>2.048879644999775</v>
+        <v>1.73150392849559</v>
       </c>
       <c r="G35">
-        <v>-6.647007179692123</v>
+        <v>-5.457726800164342</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-15.82837175911833</v>
       </c>
       <c r="E36">
-        <v>-24.56960461171775</v>
+        <v>-22.37775979336919</v>
       </c>
       <c r="F36">
-        <v>1.791232531707045</v>
+        <v>1.282979428045381</v>
       </c>
       <c r="G36">
-        <v>-5.719312866495394</v>
+        <v>-5.916929261371108</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-15.48949219075106</v>
       </c>
       <c r="E37">
-        <v>-23.88717716418385</v>
+        <v>-21.80953593183473</v>
       </c>
       <c r="F37">
-        <v>1.78286602093877</v>
+        <v>1.2644322818967</v>
       </c>
       <c r="G37">
-        <v>-5.5226002505519</v>
+        <v>-5.663391131246025</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-15.12699269048001</v>
       </c>
       <c r="E38">
-        <v>-24.30237936052512</v>
+        <v>-22.27632650407138</v>
       </c>
       <c r="F38">
-        <v>1.794133474351649</v>
+        <v>1.107744930922367</v>
       </c>
       <c r="G38">
-        <v>-5.753808751014599</v>
+        <v>-5.39913676521032</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-14.73808941440638</v>
       </c>
       <c r="E39">
-        <v>-23.40181984851575</v>
+        <v>-21.94621433433423</v>
       </c>
       <c r="F39">
-        <v>1.431361567439245</v>
+        <v>1.211299139946334</v>
       </c>
       <c r="G39">
-        <v>-4.79113852419547</v>
+        <v>-4.884585293132478</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-14.33784499945763</v>
       </c>
       <c r="E40">
-        <v>-22.81031510210785</v>
+        <v>-21.30867764963837</v>
       </c>
       <c r="F40">
-        <v>1.762829470199856</v>
+        <v>0.8013699335273592</v>
       </c>
       <c r="G40">
-        <v>-4.563515344551801</v>
+        <v>-4.770096696747863</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-13.92422118098515</v>
       </c>
       <c r="E41">
-        <v>-21.99461919300222</v>
+        <v>-20.52837629337669</v>
       </c>
       <c r="F41">
-        <v>1.556218072593603</v>
+        <v>0.9406334045512065</v>
       </c>
       <c r="G41">
-        <v>-4.657799681510244</v>
+        <v>-4.45427727339247</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-13.51110753889707</v>
       </c>
       <c r="E42">
-        <v>-21.14677111844213</v>
+        <v>-21.30017770392597</v>
       </c>
       <c r="F42">
-        <v>1.238123333183787</v>
+        <v>1.001563140496721</v>
       </c>
       <c r="G42">
-        <v>-4.141672389755709</v>
+        <v>-4.411716899939599</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-13.09813082093354</v>
       </c>
       <c r="E43">
-        <v>-21.21026938097769</v>
+        <v>-20.01479299921878</v>
       </c>
       <c r="F43">
-        <v>1.558860564608533</v>
+        <v>0.7032812926270641</v>
       </c>
       <c r="G43">
-        <v>-4.307242703811279</v>
+        <v>-4.260520974615545</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-12.6990847937803</v>
       </c>
       <c r="E44">
-        <v>-20.26221523357587</v>
+        <v>-19.57139652370575</v>
       </c>
       <c r="F44">
-        <v>0.9675536884073848</v>
+        <v>0.7340021261272865</v>
       </c>
       <c r="G44">
-        <v>-3.808005815398106</v>
+        <v>-3.674945058538179</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-12.31415595733253</v>
       </c>
       <c r="E45">
-        <v>-20.07737651000478</v>
+        <v>-19.21383727300812</v>
       </c>
       <c r="F45">
-        <v>1.225996034406803</v>
+        <v>0.4380264531070232</v>
       </c>
       <c r="G45">
-        <v>-3.708321978665111</v>
+        <v>-3.615103637370313</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-11.95490623557622</v>
       </c>
       <c r="E46">
-        <v>-19.82053957818575</v>
+        <v>-17.69611015238938</v>
       </c>
       <c r="F46">
-        <v>0.9562315627459211</v>
+        <v>0.3930933200769696</v>
       </c>
       <c r="G46">
-        <v>-3.620191945864173</v>
+        <v>-3.29474214553504</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-11.62144577769546</v>
       </c>
       <c r="E47">
-        <v>-19.1869653082466</v>
+        <v>-17.53301263252913</v>
       </c>
       <c r="F47">
-        <v>0.8984164882349325</v>
+        <v>0.1672927915848664</v>
       </c>
       <c r="G47">
-        <v>-3.169951131432213</v>
+        <v>-2.905355779205963</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-11.32283299095086</v>
       </c>
       <c r="E48">
-        <v>-19.06614562172195</v>
+        <v>-17.80133377443161</v>
       </c>
       <c r="F48">
-        <v>0.6514428889272739</v>
+        <v>0.3527725367457037</v>
       </c>
       <c r="G48">
-        <v>-2.945224679135406</v>
+        <v>-2.575536058764993</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-11.05637868359003</v>
       </c>
       <c r="E49">
-        <v>-18.40473935053166</v>
+        <v>-17.2723400832256</v>
       </c>
       <c r="F49">
-        <v>0.4926771641393178</v>
+        <v>-0.211418560892206</v>
       </c>
       <c r="G49">
-        <v>-4.255525361396785</v>
+        <v>-2.603688938030955</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-10.82402986099011</v>
       </c>
       <c r="E50">
-        <v>-18.43086864555592</v>
+        <v>-16.67052400150224</v>
       </c>
       <c r="F50">
-        <v>0.3222811610160567</v>
+        <v>-0.0666108268414216</v>
       </c>
       <c r="G50">
-        <v>-3.589721684720721</v>
+        <v>-3.10055547583801</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-10.61749029979473</v>
       </c>
       <c r="E51">
-        <v>-17.49513647592897</v>
+        <v>-16.60141495967118</v>
       </c>
       <c r="F51">
-        <v>0.2845274882660664</v>
+        <v>-0.3367157575048536</v>
       </c>
       <c r="G51">
-        <v>-3.640386273653727</v>
+        <v>-2.996557998267345</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-10.43144345374292</v>
       </c>
       <c r="E52">
-        <v>-16.43611207296919</v>
+        <v>-15.72660435086942</v>
       </c>
       <c r="F52">
-        <v>0.3332446035921082</v>
+        <v>-0.6947361489948</v>
       </c>
       <c r="G52">
-        <v>-3.728837429371975</v>
+        <v>-2.92917184381548</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-10.25457884503698</v>
       </c>
       <c r="E53">
-        <v>-15.90777048202028</v>
+        <v>-15.35802732291112</v>
       </c>
       <c r="F53">
-        <v>-0.07260572173548162</v>
+        <v>-0.4239213074671688</v>
       </c>
       <c r="G53">
-        <v>-3.619102776381752</v>
+        <v>-3.13694168186014</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-10.08124279197575</v>
       </c>
       <c r="E54">
-        <v>-15.8044669329573</v>
+        <v>-15.42654766312118</v>
       </c>
       <c r="F54">
-        <v>-0.05192967136160596</v>
+        <v>-0.4890906277802115</v>
       </c>
       <c r="G54">
-        <v>-3.722749336125255</v>
+        <v>-3.554722597279546</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-9.904520956145488</v>
       </c>
       <c r="E55">
-        <v>-15.66667452585191</v>
+        <v>-14.86590899554957</v>
       </c>
       <c r="F55">
-        <v>0.1049921075877184</v>
+        <v>-0.1234368306734677</v>
       </c>
       <c r="G55">
-        <v>-3.676481151668401</v>
+        <v>-3.390112341430365</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-9.7225636510902</v>
       </c>
       <c r="E56">
-        <v>-14.5369063019443</v>
+        <v>-15.00948426396276</v>
       </c>
       <c r="F56">
-        <v>-0.2116761831544766</v>
+        <v>-0.5618502786051061</v>
       </c>
       <c r="G56">
-        <v>-4.369818635594584</v>
+        <v>-3.406787559311673</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-9.533435796236862</v>
       </c>
       <c r="E57">
-        <v>-14.20166337115646</v>
+        <v>-13.99473927984998</v>
       </c>
       <c r="F57">
-        <v>-0.2052066337386125</v>
+        <v>-0.5088239960497013</v>
       </c>
       <c r="G57">
-        <v>-4.150994885994297</v>
+        <v>-3.35883430717533</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-9.337501476469326</v>
       </c>
       <c r="E58">
-        <v>-14.72942531743239</v>
+        <v>-13.10792368645388</v>
       </c>
       <c r="F58">
-        <v>0.1729762203354738</v>
+        <v>-0.7115329548213655</v>
       </c>
       <c r="G58">
-        <v>-4.700353433872037</v>
+        <v>-4.130929669480775</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-9.134779968656327</v>
       </c>
       <c r="E59">
-        <v>-14.08321660501184</v>
+        <v>-13.01669304909535</v>
       </c>
       <c r="F59">
-        <v>-0.1543871219442656</v>
+        <v>-0.4607588058696628</v>
       </c>
       <c r="G59">
-        <v>-4.4296137091249</v>
+        <v>-4.082344103146431</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.925426280097298</v>
       </c>
       <c r="E60">
-        <v>-13.95356186569823</v>
+        <v>-12.97441068728574</v>
       </c>
       <c r="F60">
-        <v>-0.2302548072644639</v>
+        <v>-0.6807872702990591</v>
       </c>
       <c r="G60">
-        <v>-4.538537278458</v>
+        <v>-3.573774786858051</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.710045709881042</v>
       </c>
       <c r="E61">
-        <v>-13.46723545659249</v>
+        <v>-13.40505045151916</v>
       </c>
       <c r="F61">
-        <v>-0.329347429456952</v>
+        <v>-0.6674720926664598</v>
       </c>
       <c r="G61">
-        <v>-5.341880880108625</v>
+        <v>-3.996342751127244</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.488380124687231</v>
       </c>
       <c r="E62">
-        <v>-13.32860075332167</v>
+        <v>-13.11321294409484</v>
       </c>
       <c r="F62">
-        <v>-0.3715651741406288</v>
+        <v>-0.5949940867585171</v>
       </c>
       <c r="G62">
-        <v>-5.364419074139983</v>
+        <v>-4.072932222178283</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.261508623083722</v>
       </c>
       <c r="E63">
-        <v>-12.46094060497802</v>
+        <v>-13.14163817544099</v>
       </c>
       <c r="F63">
-        <v>-0.5481631640086498</v>
+        <v>-0.8271515066997037</v>
       </c>
       <c r="G63">
-        <v>-5.107351902470036</v>
+        <v>-3.907719447040954</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.029323060726888</v>
       </c>
       <c r="E64">
-        <v>-11.82742067672696</v>
+        <v>-12.47191762597261</v>
       </c>
       <c r="F64">
-        <v>-0.5814883846232739</v>
+        <v>-0.6743533406815153</v>
       </c>
       <c r="G64">
-        <v>-5.146697736204274</v>
+        <v>-4.121209907777474</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.793587437721129</v>
       </c>
       <c r="E65">
-        <v>-12.44817030827639</v>
+        <v>-11.7112607899562</v>
       </c>
       <c r="F65">
-        <v>-0.6671929328517163</v>
+        <v>-0.5191918424631399</v>
       </c>
       <c r="G65">
-        <v>-5.46954544773954</v>
+        <v>-4.429726267673235</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.553315893905511</v>
       </c>
       <c r="E66">
-        <v>-12.33047526881703</v>
+        <v>-11.76121891520882</v>
       </c>
       <c r="F66">
-        <v>-0.7045373921047237</v>
+        <v>-0.8907038538424817</v>
       </c>
       <c r="G66">
-        <v>-4.802063324475065</v>
+        <v>-4.098602192289792</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.310703694133452</v>
       </c>
       <c r="E67">
-        <v>-12.34160625792789</v>
+        <v>-12.52689330042573</v>
       </c>
       <c r="F67">
-        <v>-0.7972814065221563</v>
+        <v>-0.8630214719757279</v>
       </c>
       <c r="G67">
-        <v>-5.418784852985895</v>
+        <v>-4.265281539101017</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.065422039626426</v>
       </c>
       <c r="E68">
-        <v>-11.29590009702466</v>
+        <v>-12.56087949785329</v>
       </c>
       <c r="F68">
-        <v>-1.005684562820664</v>
+        <v>-1.394284136984954</v>
       </c>
       <c r="G68">
-        <v>-5.293328419229674</v>
+        <v>-3.763320071709023</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-6.821951088842695</v>
       </c>
       <c r="E69">
-        <v>-11.22752013950884</v>
+        <v>-12.17206471955472</v>
       </c>
       <c r="F69">
-        <v>-0.7073936029095763</v>
+        <v>-1.246978875214729</v>
       </c>
       <c r="G69">
-        <v>-4.699148395295742</v>
+        <v>-3.966802753280327</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.581744241136987</v>
       </c>
       <c r="E70">
-        <v>-12.48672573597769</v>
+        <v>-11.77047058760649</v>
       </c>
       <c r="F70">
-        <v>-1.009209266119576</v>
+        <v>-1.370934116634842</v>
       </c>
       <c r="G70">
-        <v>-5.342261592845641</v>
+        <v>-4.042250086120317</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-6.351752261709978</v>
       </c>
       <c r="E71">
-        <v>-11.93787015777404</v>
+        <v>-12.35852916529455</v>
       </c>
       <c r="F71">
-        <v>-0.9292469607273399</v>
+        <v>-1.263407057547049</v>
       </c>
       <c r="G71">
-        <v>-4.750008306415565</v>
+        <v>-3.768428243476119</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.134435954902775</v>
       </c>
       <c r="E72">
-        <v>-11.95759619055145</v>
+        <v>-12.64815677740313</v>
       </c>
       <c r="F72">
-        <v>-0.9811947089242997</v>
+        <v>-1.159786579130859</v>
       </c>
       <c r="G72">
-        <v>-4.603430592118794</v>
+        <v>-3.98245832313554</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.93618002833852</v>
       </c>
       <c r="E73">
-        <v>-11.8450998392529</v>
+        <v>-11.80688857557618</v>
       </c>
       <c r="F73">
-        <v>-1.011300893811645</v>
+        <v>-1.352610629684917</v>
       </c>
       <c r="G73">
-        <v>-4.188930427328806</v>
+        <v>-3.600616690090463</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.757525047585683</v>
       </c>
       <c r="E74">
-        <v>-13.27801769865599</v>
+        <v>-12.66107651374701</v>
       </c>
       <c r="F74">
-        <v>-1.202555188137398</v>
+        <v>-1.776986563608715</v>
       </c>
       <c r="G74">
-        <v>-4.056488742484722</v>
+        <v>-3.48284403253089</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.602880047463683</v>
       </c>
       <c r="E75">
-        <v>-12.96074375273059</v>
+        <v>-12.30587659800737</v>
       </c>
       <c r="F75">
-        <v>-1.440816847469814</v>
+        <v>-1.737524797274152</v>
       </c>
       <c r="G75">
-        <v>-3.567590687790693</v>
+        <v>-3.081112641885871</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.468456629657893</v>
       </c>
       <c r="E76">
-        <v>-12.5242169722872</v>
+        <v>-13.14012566512243</v>
       </c>
       <c r="F76">
-        <v>-1.518161511869204</v>
+        <v>-1.850439557949753</v>
       </c>
       <c r="G76">
-        <v>-3.889345919297999</v>
+        <v>-3.736431820839063</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.35776093382312</v>
       </c>
       <c r="E77">
-        <v>-12.67756921608294</v>
+        <v>-12.92405405632044</v>
       </c>
       <c r="F77">
-        <v>-1.420969164498738</v>
+        <v>-1.840008755613701</v>
       </c>
       <c r="G77">
-        <v>-3.186573380584893</v>
+        <v>-2.557437306301797</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.26582077227473</v>
       </c>
       <c r="E78">
-        <v>-13.59411424133939</v>
+        <v>-13.6728779897548</v>
       </c>
       <c r="F78">
-        <v>-1.705739511661332</v>
+        <v>-1.988044637433195</v>
       </c>
       <c r="G78">
-        <v>-3.234162472711917</v>
+        <v>-2.477894828629728</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.197138009780442</v>
       </c>
       <c r="E79">
-        <v>-13.58928235957321</v>
+        <v>-13.9967046375693</v>
       </c>
       <c r="F79">
-        <v>-1.599118686512202</v>
+        <v>-2.129376541861833</v>
       </c>
       <c r="G79">
-        <v>-2.98345485902291</v>
+        <v>-1.726927367955913</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.146857235560815</v>
       </c>
       <c r="E80">
-        <v>-14.31925878418765</v>
+        <v>-14.69575158471135</v>
       </c>
       <c r="F80">
-        <v>-1.793634263302776</v>
+        <v>-2.302774548452839</v>
       </c>
       <c r="G80">
-        <v>-2.864503647251357</v>
+        <v>-1.934290008899242</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-5.121819284985773</v>
       </c>
       <c r="E81">
-        <v>-14.6234001554908</v>
+        <v>-15.28902243598224</v>
       </c>
       <c r="F81">
-        <v>-2.242075098645303</v>
+        <v>-2.354566563578073</v>
       </c>
       <c r="G81">
-        <v>-2.52040223335397</v>
+        <v>-2.03973088432503</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-5.11825204823612</v>
       </c>
       <c r="E82">
-        <v>-15.49488686437093</v>
+        <v>-15.73479636034929</v>
       </c>
       <c r="F82">
-        <v>-2.037010262980077</v>
+        <v>-2.658728163272801</v>
       </c>
       <c r="G82">
-        <v>-2.2150209600839</v>
+        <v>-1.826468851230719</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-5.14627168857117</v>
       </c>
       <c r="E83">
-        <v>-16.1506099006816</v>
+        <v>-16.65937037002134</v>
       </c>
       <c r="F83">
-        <v>-2.220192945332951</v>
+        <v>-2.52859495776261</v>
       </c>
       <c r="G83">
-        <v>-1.814329080738212</v>
+        <v>-1.072101460288072</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-5.203034098356147</v>
       </c>
       <c r="E84">
-        <v>-17.28970678104501</v>
+        <v>-17.10295251296868</v>
       </c>
       <c r="F84">
-        <v>-2.367920674478604</v>
+        <v>-2.997965323904269</v>
       </c>
       <c r="G84">
-        <v>-1.864646062389594</v>
+        <v>-1.172222289032251</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.301524271549893</v>
       </c>
       <c r="E85">
-        <v>-17.60967516900498</v>
+        <v>-17.47465871646628</v>
       </c>
       <c r="F85">
-        <v>-2.389425092255279</v>
+        <v>-2.99683543076685</v>
       </c>
       <c r="G85">
-        <v>-1.343099407587272</v>
+        <v>-1.233391238961364</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.439358220320565</v>
       </c>
       <c r="E86">
-        <v>-19.24183682779754</v>
+        <v>-18.90013176460076</v>
       </c>
       <c r="F86">
-        <v>-2.804423907179387</v>
+        <v>-3.221089397317927</v>
       </c>
       <c r="G86">
-        <v>-1.315330551603866</v>
+        <v>-0.8951825961238807</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.631707762145966</v>
       </c>
       <c r="E87">
-        <v>-20.50342893006843</v>
+        <v>-19.457600500367</v>
       </c>
       <c r="F87">
-        <v>-2.866722934441729</v>
+        <v>-3.05551200737675</v>
       </c>
       <c r="G87">
-        <v>-1.718068348092823</v>
+        <v>-1.024777211804191</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-5.874506759688486</v>
       </c>
       <c r="E88">
-        <v>-21.87699660912699</v>
+        <v>-21.20876139913313</v>
       </c>
       <c r="F88">
-        <v>-2.783328702899694</v>
+        <v>-3.275852766317002</v>
       </c>
       <c r="G88">
-        <v>-1.643736669099567</v>
+        <v>-0.8647255771625858</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.183000353561956</v>
       </c>
       <c r="E89">
-        <v>-22.67709645375021</v>
+        <v>-21.86030465393472</v>
       </c>
       <c r="F89">
-        <v>-3.040509445344648</v>
+        <v>-3.602914582862122</v>
       </c>
       <c r="G89">
-        <v>-1.363555268474429</v>
+        <v>-0.5835808077855195</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-6.548769207097289</v>
       </c>
       <c r="E90">
-        <v>-25.04494947135489</v>
+        <v>-24.17729837995926</v>
       </c>
       <c r="F90">
-        <v>-3.402586352006104</v>
+        <v>-3.279631778408573</v>
       </c>
       <c r="G90">
-        <v>-1.598077625021939</v>
+        <v>-0.9971275354601976</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.98505678393291</v>
       </c>
       <c r="E91">
-        <v>-25.84609086499987</v>
+        <v>-25.86753318942619</v>
       </c>
       <c r="F91">
-        <v>-3.245141873225613</v>
+        <v>-3.800302937805605</v>
       </c>
       <c r="G91">
-        <v>-2.070595100387655</v>
+        <v>-1.298728165724421</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-7.477537098676052</v>
       </c>
       <c r="E92">
-        <v>-27.59041376801441</v>
+        <v>-26.87947051965421</v>
       </c>
       <c r="F92">
-        <v>-3.252000755320793</v>
+        <v>-3.596142679344236</v>
       </c>
       <c r="G92">
-        <v>-1.361992690979893</v>
+        <v>-1.144854009059096</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-8.03588523352572</v>
       </c>
       <c r="E93">
-        <v>-28.81189717599937</v>
+        <v>-28.85177038963691</v>
       </c>
       <c r="F93">
-        <v>-3.051650986912302</v>
+        <v>-4.003327504557736</v>
       </c>
       <c r="G93">
-        <v>-2.156639489498852</v>
+        <v>-1.45489653044846</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-8.639317270481918</v>
       </c>
       <c r="E94">
-        <v>-31.53480519817545</v>
+        <v>-30.46953602955909</v>
       </c>
       <c r="F94">
-        <v>-3.045782003863467</v>
+        <v>-4.045329873716685</v>
       </c>
       <c r="G94">
-        <v>-2.539861620033806</v>
+        <v>-2.329976343389553</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.290372576567576</v>
       </c>
       <c r="E95">
-        <v>-33.86544095214809</v>
+        <v>-33.32859488701278</v>
       </c>
       <c r="F95">
-        <v>-2.995727075181904</v>
+        <v>-4.179717574207654</v>
       </c>
       <c r="G95">
-        <v>-3.075680036655926</v>
+        <v>-2.398938317518111</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.969415686300032</v>
       </c>
       <c r="E96">
-        <v>-35.37997323435442</v>
+        <v>-35.52344208362842</v>
       </c>
       <c r="F96">
-        <v>-3.315943263510289</v>
+        <v>-3.726072106473339</v>
       </c>
       <c r="G96">
-        <v>-3.03314945811291</v>
+        <v>-3.340285320518794</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-10.67021383227451</v>
       </c>
       <c r="E97">
-        <v>-37.91350273776673</v>
+        <v>-37.25776838027104</v>
       </c>
       <c r="F97">
-        <v>-3.2186846467476</v>
+        <v>-4.130192800663883</v>
       </c>
       <c r="G97">
-        <v>-3.930823744359528</v>
+        <v>-2.717306860938742</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-11.38529103373896</v>
       </c>
       <c r="E98">
-        <v>-40.26406151313611</v>
+        <v>-39.67831019295497</v>
       </c>
       <c r="F98">
-        <v>-3.040404242684493</v>
+        <v>-3.957441749014463</v>
       </c>
       <c r="G98">
-        <v>-4.015040712333048</v>
+        <v>-4.016798612014401</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-12.09484951656663</v>
       </c>
       <c r="E99">
-        <v>-43.04889188889308</v>
+        <v>-42.52526670362316</v>
       </c>
       <c r="F99">
-        <v>-2.916859043128766</v>
+        <v>-4.064826328908974</v>
       </c>
       <c r="G99">
-        <v>-4.754848323993979</v>
+        <v>-4.417132952441847</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-12.82184542250241</v>
       </c>
       <c r="E100">
-        <v>-45.25710034806836</v>
+        <v>-44.68786210835618</v>
       </c>
       <c r="F100">
-        <v>-2.944772539500901</v>
+        <v>-3.995553276482463</v>
       </c>
       <c r="G100">
-        <v>-4.909281962855441</v>
+        <v>-4.572278358594252</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-13.51426711015462</v>
       </c>
       <c r="E101">
-        <v>-47.48997540516341</v>
+        <v>-46.57951891321028</v>
       </c>
       <c r="F101">
-        <v>-2.893565351762044</v>
+        <v>-4.162668116323235</v>
       </c>
       <c r="G101">
-        <v>-5.202765135457371</v>
+        <v>-5.492517323236543</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-14.27230807394697</v>
       </c>
       <c r="E102">
-        <v>-49.77745480184296</v>
+        <v>-49.08192534688637</v>
       </c>
       <c r="F102">
-        <v>-2.910715042102202</v>
+        <v>-4.01967119341497</v>
       </c>
       <c r="G102">
-        <v>-5.587774960583531</v>
+        <v>-5.180663933437197</v>
       </c>
     </row>
   </sheetData>
